--- a/ITI/MHD/StructureDefinition-IHE.MHD.FindDocumentListsResponseMessage.xlsx
+++ b/ITI/MHD/StructureDefinition-IHE.MHD.FindDocumentListsResponseMessage.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>4.2.3</t>
+    <t>4.2.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-31T14:38:46-05:00</t>
+    <t>2026-06-15T14:55:16-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -586,7 +586,7 @@
 </t>
   </si>
   <si>
-    <t>closed</t>
+    <t>open</t>
   </si>
   <si>
     <t>bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}
@@ -3762,7 +3762,7 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>187</v>

--- a/ITI/MHD/StructureDefinition-IHE.MHD.FindDocumentListsResponseMessage.xlsx
+++ b/ITI/MHD/StructureDefinition-IHE.MHD.FindDocumentListsResponseMessage.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>4.2.4</t>
+    <t>4.2.5-comment</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T14:55:16-05:00</t>
+    <t>2026-06-16T19:25:56-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
